--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12210"/>
+    <workbookView windowWidth="27945" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,16 +40,16 @@
     <t>I'm fine too too.</t>
   </si>
   <si>
-    <t>I'm fine too too too.</t>
-  </si>
-  <si>
-    <t>I'm fine four too.</t>
-  </si>
-  <si>
-    <t>Son of xxxxx</t>
-  </si>
-  <si>
-    <t>Bye idiot</t>
+    <t>早上好，我的朋友们</t>
+  </si>
+  <si>
+    <t>早上好呀，你刚刚都吃了啥</t>
+  </si>
+  <si>
+    <t>おはようございます。</t>
+  </si>
+  <si>
+    <t>こんにちは</t>
   </si>
 </sst>
 </file>

--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11760"/>
+    <workbookView windowWidth="11385" windowHeight="8310"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>playerA</t>
   </si>
@@ -22,12 +22,48 @@
     <t>Hello!</t>
   </si>
   <si>
+    <t>Annie</t>
+  </si>
+  <si>
+    <t>audio1</t>
+  </si>
+  <si>
     <t>playerB</t>
   </si>
   <si>
     <t>Hi!</t>
   </si>
   <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>audio2</t>
+  </si>
+  <si>
+    <t>早上好，我的朋友们！</t>
+  </si>
+  <si>
+    <t>audio3</t>
+  </si>
+  <si>
+    <t>早上好呀，你刚刚都吃了什么？</t>
+  </si>
+  <si>
+    <t>audio4</t>
+  </si>
+  <si>
+    <t>おはようございます。</t>
+  </si>
+  <si>
+    <t>audio5</t>
+  </si>
+  <si>
+    <t>こんにちは。</t>
+  </si>
+  <si>
+    <t>audio6</t>
+  </si>
+  <si>
     <t>How old are you?</t>
   </si>
   <si>
@@ -38,18 +74,6 @@
   </si>
   <si>
     <t>I'm fine too too.</t>
-  </si>
-  <si>
-    <t>早上好，我的朋友们</t>
-  </si>
-  <si>
-    <t>早上好呀，你刚刚都吃了啥</t>
-  </si>
-  <si>
-    <t>おはようございます。</t>
-  </si>
-  <si>
-    <t>こんにちは</t>
   </si>
 </sst>
 </file>
@@ -984,91 +1008,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="45.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11385" windowHeight="8310"/>
+    <workbookView windowWidth="27945" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>Avatar</t>
+  </si>
+  <si>
+    <t>Vocal</t>
+  </si>
+  <si>
+    <t>BGimage</t>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
   <si>
     <t>playerA</t>
   </si>
@@ -26,6 +44,9 @@
   </si>
   <si>
     <t>audio1</t>
+  </si>
+  <si>
+    <t>bgm1</t>
   </si>
   <si>
     <t>playerB</t>
@@ -86,10 +107,17 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -557,138 +585,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1008,140 +1051,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="45.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="17.7142857142857" style="2" customWidth="1"/>
+    <col min="2" max="2" width="45.1428571428571" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.7142857142857" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.1428571428571" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.8571428571429" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2</v>
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="A10" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -34,6 +34,24 @@
     <t>BGM</t>
   </si>
   <si>
+    <t>Charater1Action</t>
+  </si>
+  <si>
+    <t>Charater1Img</t>
+  </si>
+  <si>
+    <t>Charater2Action</t>
+  </si>
+  <si>
+    <t>Charater2Img</t>
+  </si>
+  <si>
+    <t>bgm1</t>
+  </si>
+  <si>
+    <t>disappear</t>
+  </si>
+  <si>
     <t>playerA</t>
   </si>
   <si>
@@ -46,7 +64,7 @@
     <t>audio1</t>
   </si>
   <si>
-    <t>bgm1</t>
+    <t>appearAt(x,y)</t>
   </si>
   <si>
     <t>playerB</t>
@@ -65,6 +83,9 @@
   </si>
   <si>
     <t>audio3</t>
+  </si>
+  <si>
+    <t>moveTo(x,y)</t>
   </si>
   <si>
     <t>早上好呀，你刚刚都吃了什么？</t>
@@ -715,7 +736,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -725,9 +746,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1051,8 +1069,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7142857142857" style="2" customWidth="1"/>
     <col min="2" max="2" width="45.1428571428571" style="2" customWidth="1"/>
@@ -1060,164 +1078,213 @@
     <col min="4" max="4" width="18.7142857142857" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.1428571428571" style="3" customWidth="1"/>
     <col min="6" max="6" width="13.8571428571429" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="23.2857142857143" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.7142857142857" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.1428571428571" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.4285714285714" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3">
-        <v>3</v>
-      </c>
+    <row r="2" s="1" customFormat="1" spans="5:9">
+      <c r="E2" s="4"/>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="E9" s="3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
   <si>
     <t>Name</t>
   </si>
@@ -37,67 +37,79 @@
     <t>Charater1Action</t>
   </si>
   <si>
+    <t>x1</t>
+  </si>
+  <si>
     <t>Charater1Img</t>
   </si>
   <si>
     <t>Charater2Action</t>
   </si>
   <si>
+    <t>x2</t>
+  </si>
+  <si>
     <t>Charater2Img</t>
   </si>
   <si>
     <t>bgm1</t>
   </si>
   <si>
+    <t>playerA</t>
+  </si>
+  <si>
+    <t>Hello!</t>
+  </si>
+  <si>
+    <t>Annie</t>
+  </si>
+  <si>
+    <t>audio1</t>
+  </si>
+  <si>
+    <t>appearAt</t>
+  </si>
+  <si>
+    <t>playerB</t>
+  </si>
+  <si>
+    <t>Hi!</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>audio2</t>
+  </si>
+  <si>
+    <t>appearAt(x,y)</t>
+  </si>
+  <si>
+    <t>早上好，我的朋友们！</t>
+  </si>
+  <si>
+    <t>audio3</t>
+  </si>
+  <si>
+    <t>moveTo</t>
+  </si>
+  <si>
+    <t>早上好呀，你刚刚都吃了什么？</t>
+  </si>
+  <si>
+    <t>audio4</t>
+  </si>
+  <si>
+    <t>moveTo(x,y)</t>
+  </si>
+  <si>
+    <t>おはようございます。</t>
+  </si>
+  <si>
+    <t>audio5</t>
+  </si>
+  <si>
     <t>disappear</t>
-  </si>
-  <si>
-    <t>playerA</t>
-  </si>
-  <si>
-    <t>Hello!</t>
-  </si>
-  <si>
-    <t>Annie</t>
-  </si>
-  <si>
-    <t>audio1</t>
-  </si>
-  <si>
-    <t>appearAt(x,y)</t>
-  </si>
-  <si>
-    <t>playerB</t>
-  </si>
-  <si>
-    <t>Hi!</t>
-  </si>
-  <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>audio2</t>
-  </si>
-  <si>
-    <t>早上好，我的朋友们！</t>
-  </si>
-  <si>
-    <t>audio3</t>
-  </si>
-  <si>
-    <t>moveTo(x,y)</t>
-  </si>
-  <si>
-    <t>早上好呀，你刚刚都吃了什么？</t>
-  </si>
-  <si>
-    <t>audio4</t>
-  </si>
-  <si>
-    <t>おはようございます。</t>
-  </si>
-  <si>
-    <t>audio5</t>
   </si>
   <si>
     <t>こんにちは。</t>
@@ -739,15 +751,15 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1069,23 +1081,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.7142857142857" style="2" customWidth="1"/>
-    <col min="2" max="2" width="45.1428571428571" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.7142857142857" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.7142857142857" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.1428571428571" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.8571428571429" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.2857142857143" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.7142857142857" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18.1428571428571" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.4285714285714" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="17.7142857142857" style="3" customWidth="1"/>
+    <col min="2" max="2" width="45.1428571428571" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.7142857142857" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.7142857142857" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.1428571428571" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.8571428571429" style="4" customWidth="1"/>
+    <col min="7" max="7" width="23.2857142857143" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.7142857142857" style="3" customWidth="1"/>
+    <col min="10" max="10" width="18.1428571428571" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.85714285714286" style="4" customWidth="1"/>
+    <col min="12" max="12" width="18.4285714285714" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1098,10 +1112,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1116,175 +1130,190 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="5:9">
-      <c r="E2" s="4"/>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
+    <row r="2" s="2" customFormat="1" spans="5:11">
+      <c r="E2" s="4">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>19</v>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="2" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="4">
+        <v>300</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>23</v>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="4">
+        <v>-300</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>11</v>
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>11</v>
+    <row r="8" spans="1:10">
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>14</v>
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -118,16 +118,13 @@
     <t>audio6</t>
   </si>
   <si>
-    <t>How old are you?</t>
-  </si>
-  <si>
-    <t>I'm fine, thand you and you.</t>
-  </si>
-  <si>
-    <t>I'm fine too.</t>
-  </si>
-  <si>
-    <t>I'm fine too too.</t>
+    <t>CHOICE</t>
+  </si>
+  <si>
+    <t>choice1</t>
+  </si>
+  <si>
+    <t>choice2</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7142857142857" style="3" customWidth="1"/>
@@ -1271,49 +1268,19 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E9" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Project_VN learning/Assets/Resources/story/1.xlsx
+++ b/Project_VN learning/Assets/Resources/story/1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -1078,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7142857142857" style="3" customWidth="1"/>
@@ -1266,20 +1266,260 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:9">
       <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="4">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="4">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E21" s="4">
         <v>3</v>
       </c>
     </row>
